--- a/Deliverables/Bracelet(Main)/BOM/Bracelet_Main-PCB(Digikey).xlsx
+++ b/Deliverables/Bracelet(Main)/BOM/Bracelet_Main-PCB(Digikey).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Main)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB72D6C-E217-46B9-98FD-81ABEFC484BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EAF4F9-6D00-4AE0-8647-FF2CFE388350}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1810,6 +1810,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1817,6 +1826,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1824,21 +1839,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2145,25 +2145,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="110" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="117"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="112"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2222,7 +2222,7 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="113" t="s">
         <v>247</v>
       </c>
       <c r="C3" s="44" t="s">
@@ -2276,7 +2276,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="111"/>
+      <c r="B4" s="114"/>
       <c r="C4" s="45" t="s">
         <v>8</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="111"/>
+      <c r="B5" s="114"/>
       <c r="C5" s="45" t="s">
         <v>13</v>
       </c>
@@ -2380,7 +2380,7 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="111"/>
+      <c r="B6" s="114"/>
       <c r="C6" s="46" t="s">
         <v>268</v>
       </c>
@@ -2432,7 +2432,7 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="111"/>
+      <c r="B7" s="114"/>
       <c r="C7" s="46" t="s">
         <v>269</v>
       </c>
@@ -2484,7 +2484,7 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="111"/>
+      <c r="B8" s="114"/>
       <c r="C8" s="45" t="s">
         <v>24</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="111"/>
+      <c r="B9" s="114"/>
       <c r="C9" s="46" t="s">
         <v>270</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="111"/>
+      <c r="B10" s="114"/>
       <c r="C10" s="46" t="s">
         <v>271</v>
       </c>
@@ -2640,7 +2640,7 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="111"/>
+      <c r="B11" s="114"/>
       <c r="C11" s="45" t="s">
         <v>34</v>
       </c>
@@ -2692,7 +2692,7 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="112"/>
+      <c r="B12" s="115"/>
       <c r="C12" s="47" t="s">
         <v>38</v>
       </c>
@@ -2744,7 +2744,7 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="116" t="s">
         <v>248</v>
       </c>
       <c r="C13" s="48" t="s">
@@ -2800,7 +2800,7 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="111"/>
+      <c r="B14" s="114"/>
       <c r="C14" s="45" t="s">
         <v>46</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="119"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="55" t="s">
         <v>275</v>
       </c>
@@ -2906,7 +2906,7 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="113" t="s">
         <v>249</v>
       </c>
       <c r="C16" s="60" t="s">
@@ -2962,7 +2962,7 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="111"/>
+      <c r="B17" s="114"/>
       <c r="C17" s="49" t="s">
         <v>294</v>
       </c>
@@ -3016,7 +3016,7 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="111"/>
+      <c r="B18" s="114"/>
       <c r="C18" s="45" t="s">
         <v>69</v>
       </c>
@@ -3070,7 +3070,7 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="112"/>
+      <c r="B19" s="115"/>
       <c r="C19" s="61" t="s">
         <v>276</v>
       </c>
@@ -3124,7 +3124,7 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="116" t="s">
         <v>250</v>
       </c>
       <c r="C20" s="48" t="s">
@@ -3178,7 +3178,7 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="119"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="67" t="s">
         <v>87</v>
       </c>
@@ -3230,7 +3230,7 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="113" t="s">
         <v>251</v>
       </c>
       <c r="C22" s="69" t="s">
@@ -3284,7 +3284,7 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="111"/>
+      <c r="B23" s="114"/>
       <c r="C23" s="46" t="s">
         <v>281</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="111"/>
+      <c r="B24" s="114"/>
       <c r="C24" s="46" t="s">
         <v>280</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="111"/>
+      <c r="B25" s="114"/>
       <c r="C25" s="46" t="s">
         <v>282</v>
       </c>
@@ -3440,7 +3440,7 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="111"/>
+      <c r="B26" s="114"/>
       <c r="C26" s="46" t="s">
         <v>283</v>
       </c>
@@ -3492,7 +3492,7 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="111"/>
+      <c r="B27" s="114"/>
       <c r="C27" s="45" t="s">
         <v>107</v>
       </c>
@@ -3544,7 +3544,7 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="111"/>
+      <c r="B28" s="114"/>
       <c r="C28" s="46" t="s">
         <v>284</v>
       </c>
@@ -3596,7 +3596,7 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="111"/>
+      <c r="B29" s="114"/>
       <c r="C29" s="46" t="s">
         <v>285</v>
       </c>
@@ -3648,7 +3648,7 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="111"/>
+      <c r="B30" s="114"/>
       <c r="C30" s="46" t="s">
         <v>286</v>
       </c>
@@ -3700,7 +3700,7 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="111"/>
+      <c r="B31" s="114"/>
       <c r="C31" s="45" t="s">
         <v>120</v>
       </c>
@@ -3752,7 +3752,7 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="111"/>
+      <c r="B32" s="114"/>
       <c r="C32" s="46" t="s">
         <v>287</v>
       </c>
@@ -3804,7 +3804,7 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="111"/>
+      <c r="B33" s="114"/>
       <c r="C33" s="45" t="s">
         <v>126</v>
       </c>
@@ -3856,7 +3856,7 @@
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="112"/>
+      <c r="B34" s="115"/>
       <c r="C34" s="61" t="s">
         <v>288</v>
       </c>
@@ -4018,7 +4018,7 @@
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="110" t="s">
+      <c r="B37" s="113" t="s">
         <v>254</v>
       </c>
       <c r="C37" s="60" t="s">
@@ -4074,7 +4074,7 @@
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="111"/>
+      <c r="B38" s="114"/>
       <c r="C38" s="45" t="s">
         <v>295</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="111"/>
+      <c r="B39" s="114"/>
       <c r="C39" s="45" t="s">
         <v>146</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="111"/>
+      <c r="B40" s="114"/>
       <c r="C40" s="45" t="s">
         <v>150</v>
       </c>
@@ -4234,7 +4234,7 @@
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="111"/>
+      <c r="B41" s="114"/>
       <c r="C41" s="45" t="s">
         <v>154</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="111"/>
+      <c r="B42" s="114"/>
       <c r="C42" s="45" t="s">
         <v>297</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="111"/>
+      <c r="B43" s="114"/>
       <c r="C43" s="45" t="s">
         <v>161</v>
       </c>
@@ -4396,7 +4396,7 @@
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="111"/>
+      <c r="B44" s="114"/>
       <c r="C44" s="45" t="s">
         <v>165</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="112"/>
+      <c r="B45" s="115"/>
       <c r="C45" s="70" t="s">
         <v>169</v>
       </c>
@@ -4502,7 +4502,7 @@
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="110" t="s">
+      <c r="B46" s="113" t="s">
         <v>255</v>
       </c>
       <c r="C46" s="60" t="s">
@@ -4558,7 +4558,7 @@
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="111"/>
+      <c r="B47" s="114"/>
       <c r="C47" s="45" t="s">
         <v>296</v>
       </c>
@@ -4612,7 +4612,7 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="111"/>
+      <c r="B48" s="114"/>
       <c r="C48" s="45" t="s">
         <v>58</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="111"/>
+      <c r="B49" s="114"/>
       <c r="C49" s="45" t="s">
         <v>52</v>
       </c>
@@ -4716,7 +4716,7 @@
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="111"/>
+      <c r="B50" s="114"/>
       <c r="C50" s="45" t="s">
         <v>55</v>
       </c>
@@ -4768,7 +4768,7 @@
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="111"/>
+      <c r="B51" s="114"/>
       <c r="C51" s="45" t="s">
         <v>79</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="112"/>
+      <c r="B52" s="115"/>
       <c r="C52" s="89" t="s">
         <v>133</v>
       </c>
@@ -4943,24 +4943,24 @@
       </c>
     </row>
     <row r="55" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J55" s="113" t="s">
+      <c r="J55" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="K55" s="113"/>
-      <c r="L55" s="113"/>
-      <c r="M55" s="113"/>
+      <c r="K55" s="118"/>
+      <c r="L55" s="118"/>
+      <c r="M55" s="118"/>
       <c r="P55" s="19">
         <f>SUM(P3:P47)</f>
         <v>247.77164999999997</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J56" s="114" t="s">
+      <c r="J56" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="K56" s="114"/>
-      <c r="L56" s="114"/>
-      <c r="M56" s="114"/>
+      <c r="K56" s="119"/>
+      <c r="L56" s="119"/>
+      <c r="M56" s="119"/>
       <c r="N56" s="18">
         <f>SUM(N3:N47)</f>
         <v>53.327129999999997</v>
@@ -4972,16 +4972,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B22:B34"/>
+    <mergeCell ref="B37:B45"/>
+    <mergeCell ref="B46:B52"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="J56:M56"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B3:B12"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B34"/>
-    <mergeCell ref="B37:B45"/>
-    <mergeCell ref="B46:B52"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
   </mergeCells>
   <conditionalFormatting sqref="N56:P56">
     <cfRule type="dataBar" priority="5">

--- a/Deliverables/Bracelet(Main)/BOM/Bracelet_Main-PCB(Digikey).xlsx
+++ b/Deliverables/Bracelet(Main)/BOM/Bracelet_Main-PCB(Digikey).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20361"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Main)\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Main)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EAF4F9-6D00-4AE0-8647-FF2CFE388350}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="Brac_PCB" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="301">
   <si>
     <t>Description</t>
   </si>
@@ -802,9 +801,6 @@
   </si>
   <si>
     <t>Display Module</t>
-  </si>
-  <si>
-    <t>Quotation Send to supplier</t>
   </si>
   <si>
     <t>Battery</t>
@@ -939,12 +935,24 @@
   </si>
   <si>
     <t>Step-Up Positive Adjustable SOT-23-6 DC-DC Converters</t>
+  </si>
+  <si>
+    <t>Quantity 25</t>
+  </si>
+  <si>
+    <t>Unit Cost (25 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1073,7 +1081,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1110,26 +1118,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1318,77 +1306,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -1497,6 +1414,56 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1517,7 +1484,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1561,13 +1528,13 @@
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1575,275 +1542,263 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Hyperlink 2" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2121,112 +2076,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="110" t="s">
-        <v>264</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="112"/>
+    <row r="1" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="113" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="115"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="E2" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="97" t="s">
+      <c r="F2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G2" s="105" t="s">
         <v>175</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="105" t="s">
         <v>176</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="105" t="s">
         <v>177</v>
       </c>
-      <c r="J2" s="97" t="s">
+      <c r="J2" s="105" t="s">
         <v>178</v>
       </c>
-      <c r="K2" s="97" t="s">
+      <c r="K2" s="105" t="s">
         <v>179</v>
       </c>
-      <c r="L2" s="97" t="s">
+      <c r="L2" s="105" t="s">
+        <v>297</v>
+      </c>
+      <c r="M2" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="M2" s="97" t="s">
+      <c r="N2" s="105" t="s">
         <v>181</v>
       </c>
-      <c r="N2" s="97" t="s">
+      <c r="O2" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="O2" s="97" t="s">
+      <c r="P2" s="105" t="s">
         <v>183</v>
       </c>
-      <c r="P2" s="97" t="s">
+      <c r="Q2" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="Q2" s="97" t="s">
+      <c r="R2" s="105" t="s">
+        <v>298</v>
+      </c>
+      <c r="S2" s="105" t="s">
+        <v>299</v>
+      </c>
+      <c r="T2" s="105" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="110" t="s">
         <v>247</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D3" s="27" t="s">
         <v>4</v>
@@ -2241,7 +2211,7 @@
         <v>186</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I3" s="28" t="s">
         <v>3</v>
@@ -2253,30 +2223,41 @@
         <f>J3*5</f>
         <v>120</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="29">
+        <f>J3*25</f>
+        <v>600</v>
+      </c>
+      <c r="M3" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M3" s="33">
+      <c r="N3" s="33">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="N3" s="33">
-        <f>M3*J3</f>
+      <c r="O3" s="33">
+        <f>N3*J3</f>
         <v>1.3440000000000001</v>
       </c>
-      <c r="O3" s="33">
+      <c r="P3" s="33">
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="P3" s="34">
-        <f>O3*K3</f>
+      <c r="Q3" s="34">
+        <f>P3*K3</f>
         <v>2.976</v>
       </c>
-      <c r="Q3" s="35"/>
+      <c r="R3" s="34">
+        <v>1.772E-2</v>
+      </c>
+      <c r="S3" s="34">
+        <f>R3*L3</f>
+        <v>10.632</v>
+      </c>
+      <c r="T3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="114"/>
+      <c r="B4" s="111"/>
       <c r="C4" s="45" t="s">
         <v>8</v>
       </c>
@@ -2293,7 +2274,7 @@
         <v>188</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>7</v>
@@ -2305,30 +2286,41 @@
         <f t="shared" ref="K4:K52" si="0">J4*5</f>
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L53" si="1">J4*25</f>
+        <v>25</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>0.1</v>
       </c>
-      <c r="N4" s="13">
-        <f t="shared" ref="N4:N47" si="1">M4*J4</f>
+      <c r="O4" s="13">
+        <f>N4*J4</f>
         <v>0.1</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>0.1</v>
       </c>
-      <c r="P4" s="11">
-        <f t="shared" ref="P4:P47" si="2">O4*K4</f>
+      <c r="Q4" s="11">
+        <f>P4*K4</f>
         <v>0.5</v>
       </c>
-      <c r="Q4" s="36"/>
+      <c r="R4" s="11">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="S4" s="11">
+        <f>R4*L4</f>
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="T4" s="36"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="114"/>
+      <c r="B5" s="111"/>
       <c r="C5" s="45" t="s">
         <v>13</v>
       </c>
@@ -2345,7 +2337,7 @@
         <v>188</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>12</v>
@@ -2357,32 +2349,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>0.1</v>
       </c>
-      <c r="N5" s="13">
-        <f t="shared" si="1"/>
+      <c r="O5" s="13">
+        <f>N5*J5</f>
         <v>0.1</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>0.1</v>
       </c>
-      <c r="P5" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q5" s="11">
+        <f>P5*K5</f>
         <v>0.5</v>
       </c>
-      <c r="Q5" s="36"/>
+      <c r="R5" s="11">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="S5" s="11">
+        <f>R5*L5</f>
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="T5" s="36"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="114"/>
+      <c r="B6" s="111"/>
       <c r="C6" s="46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -2409,32 +2412,43 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="4">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>0.37</v>
       </c>
-      <c r="N6" s="13">
-        <f t="shared" si="1"/>
+      <c r="O6" s="13">
+        <f>N6*J6</f>
         <v>2.2199999999999998</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>0.25800000000000001</v>
       </c>
-      <c r="P6" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q6" s="11">
+        <f>P6*K6</f>
         <v>7.74</v>
       </c>
-      <c r="Q6" s="36"/>
+      <c r="R6" s="11">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="S6" s="11">
+        <f>R6*L6</f>
+        <v>23.189999999999998</v>
+      </c>
+      <c r="T6" s="36"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
+      <c r="B7" s="111"/>
       <c r="C7" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>21</v>
@@ -2461,30 +2475,41 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="4">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N7" s="13">
-        <f t="shared" si="1"/>
+      <c r="O7" s="13">
+        <f>N7*J7</f>
         <v>1.4000000000000001</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>0.193</v>
       </c>
-      <c r="P7" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q7" s="11">
+        <f>P7*K7</f>
         <v>4.8250000000000002</v>
       </c>
-      <c r="Q7" s="36"/>
+      <c r="R7" s="11">
+        <v>9.7900000000000001E-2</v>
+      </c>
+      <c r="S7" s="11">
+        <f>R7*L7</f>
+        <v>12.237500000000001</v>
+      </c>
+      <c r="T7" s="36"/>
     </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="114"/>
+      <c r="B8" s="111"/>
       <c r="C8" s="45" t="s">
         <v>24</v>
       </c>
@@ -2501,7 +2526,7 @@
         <v>189</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>23</v>
@@ -2513,32 +2538,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>0.3</v>
       </c>
-      <c r="N8" s="13">
-        <f t="shared" si="1"/>
+      <c r="O8" s="13">
+        <f>N8*J8</f>
         <v>0.3</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>0.3</v>
       </c>
-      <c r="P8" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q8" s="11">
+        <f>P8*K8</f>
         <v>1.5</v>
       </c>
-      <c r="Q8" s="36"/>
+      <c r="R8" s="11">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="S8" s="11">
+        <f>R8*L8</f>
+        <v>5.2249999999999996</v>
+      </c>
+      <c r="T8" s="36"/>
     </row>
-    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="114"/>
+      <c r="B9" s="111"/>
       <c r="C9" s="46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>28</v>
@@ -2565,32 +2601,43 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="4">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>0.54</v>
       </c>
-      <c r="N9" s="13">
-        <f t="shared" si="1"/>
+      <c r="O9" s="13">
+        <f>N9*J9</f>
         <v>1.62</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>0.38100000000000001</v>
       </c>
-      <c r="P9" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q9" s="11">
+        <f>P9*K9</f>
         <v>5.7149999999999999</v>
       </c>
-      <c r="Q9" s="36"/>
+      <c r="R9" s="11">
+        <v>0.28839999999999999</v>
+      </c>
+      <c r="S9" s="11">
+        <f>R9*L9</f>
+        <v>21.63</v>
+      </c>
+      <c r="T9" s="36"/>
     </row>
-    <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="114"/>
+      <c r="B10" s="111"/>
       <c r="C10" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
@@ -2617,30 +2664,41 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N10" s="13">
-        <f t="shared" si="1"/>
+      <c r="O10" s="13">
+        <f>N10*J10</f>
         <v>1.1599999999999999</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>0.19700000000000001</v>
       </c>
-      <c r="P10" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q10" s="11">
+        <f>P10*K10</f>
         <v>3.9400000000000004</v>
       </c>
-      <c r="Q10" s="36"/>
+      <c r="R10" s="11">
+        <v>0.1118</v>
+      </c>
+      <c r="S10" s="11">
+        <f>R10*L10</f>
+        <v>11.18</v>
+      </c>
+      <c r="T10" s="36"/>
     </row>
-    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="114"/>
+      <c r="B11" s="111"/>
       <c r="C11" s="45" t="s">
         <v>34</v>
       </c>
@@ -2669,30 +2727,41 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>0.31</v>
       </c>
-      <c r="N11" s="13">
-        <f t="shared" si="1"/>
+      <c r="O11" s="13">
+        <f>N11*J11</f>
         <v>0.62</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>0.20899999999999999</v>
       </c>
-      <c r="P11" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q11" s="11">
+        <f>P11*K11</f>
         <v>2.09</v>
       </c>
-      <c r="Q11" s="36"/>
+      <c r="R11" s="11">
+        <v>0.12520000000000001</v>
+      </c>
+      <c r="S11" s="11">
+        <f>R11*L11</f>
+        <v>6.2600000000000007</v>
+      </c>
+      <c r="T11" s="36"/>
     </row>
-    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="115"/>
+      <c r="B12" s="112"/>
       <c r="C12" s="47" t="s">
         <v>38</v>
       </c>
@@ -2721,86 +2790,108 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L12" s="40" t="s">
+      <c r="L12" s="51">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M12" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="M12" s="41">
+      <c r="N12" s="41">
         <v>0.1</v>
       </c>
-      <c r="N12" s="41">
-        <f t="shared" si="1"/>
+      <c r="O12" s="41">
+        <f>N12*J12</f>
         <v>0.1</v>
       </c>
-      <c r="O12" s="41">
+      <c r="P12" s="41">
         <v>0.1</v>
       </c>
-      <c r="P12" s="42">
-        <f t="shared" si="2"/>
+      <c r="Q12" s="42">
+        <f>P12*K12</f>
         <v>0.5</v>
       </c>
-      <c r="Q12" s="43"/>
+      <c r="R12" s="42">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="S12" s="64">
+        <f>R12*L12</f>
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="T12" s="43"/>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="116" t="s">
+      <c r="B13" s="110" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="J13" s="23">
+      <c r="I13" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="J13" s="31">
         <v>1</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="29">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M13" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M13" s="25">
+      <c r="N13" s="33">
         <v>0.42</v>
       </c>
-      <c r="N13" s="25">
-        <f t="shared" si="1"/>
+      <c r="O13" s="33">
+        <f>N13*J13</f>
         <v>0.42</v>
       </c>
-      <c r="O13" s="25">
+      <c r="P13" s="33">
         <v>0.42</v>
       </c>
-      <c r="P13" s="26">
-        <f t="shared" si="2"/>
+      <c r="Q13" s="34">
+        <f>P13*K13</f>
         <v>2.1</v>
       </c>
-      <c r="Q13" s="98" t="s">
+      <c r="R13" s="34">
+        <v>0.313</v>
+      </c>
+      <c r="S13" s="34">
+        <f>R13*L13</f>
+        <v>7.8250000000000002</v>
+      </c>
+      <c r="T13" s="97" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="114"/>
+      <c r="B14" s="111"/>
       <c r="C14" s="45" t="s">
         <v>46</v>
       </c>
@@ -2808,7 +2899,7 @@
         <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>45</v>
@@ -2817,10 +2908,10 @@
         <v>190</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J14" s="5">
         <v>1</v>
@@ -2829,94 +2920,116 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>0.46</v>
       </c>
-      <c r="N14" s="13">
-        <f t="shared" si="1"/>
+      <c r="O14" s="13">
+        <f>N14*J14</f>
         <v>0.46</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>0.46</v>
       </c>
-      <c r="P14" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q14" s="11">
+        <f>P14*K14</f>
         <v>2.3000000000000003</v>
       </c>
-      <c r="Q14" s="99" t="s">
+      <c r="R14" s="11">
+        <v>0.376</v>
+      </c>
+      <c r="S14" s="11">
+        <f>R14*L14</f>
+        <v>9.4</v>
+      </c>
+      <c r="T14" s="96" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="55" t="s">
-        <v>275</v>
-      </c>
-      <c r="D15" s="15" t="s">
+      <c r="B15" s="112"/>
+      <c r="C15" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="I15" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="J15" s="61">
         <v>2</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="51">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L15" s="56" t="s">
+      <c r="L15" s="51">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M15" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="M15" s="57">
+      <c r="N15" s="63">
         <v>0.38</v>
       </c>
-      <c r="N15" s="57">
-        <f t="shared" si="1"/>
+      <c r="O15" s="63">
+        <f>N15*J15</f>
         <v>0.76</v>
       </c>
-      <c r="O15" s="57">
+      <c r="P15" s="63">
         <v>0.248</v>
       </c>
-      <c r="P15" s="58">
-        <f t="shared" si="2"/>
+      <c r="Q15" s="64">
+        <f>P15*K15</f>
         <v>2.48</v>
       </c>
-      <c r="Q15" s="100"/>
+      <c r="R15" s="64">
+        <v>0.248</v>
+      </c>
+      <c r="S15" s="64">
+        <f>R15*L15</f>
+        <v>12.4</v>
+      </c>
+      <c r="T15" s="102"/>
     </row>
-    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="110" t="s">
         <v>249</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="58" t="s">
         <v>63</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F16" s="28" t="s">
         <v>65</v>
@@ -2937,40 +3050,51 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="L16" s="29">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M16" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M16" s="33">
+      <c r="N16" s="33">
         <v>0.74</v>
       </c>
-      <c r="N16" s="33">
-        <f t="shared" si="1"/>
+      <c r="O16" s="33">
+        <f>N16*J16</f>
         <v>0.74</v>
       </c>
-      <c r="O16" s="33">
+      <c r="P16" s="33">
         <v>0.74</v>
       </c>
-      <c r="P16" s="34">
-        <f t="shared" si="2"/>
+      <c r="Q16" s="34">
+        <f>P16*K16</f>
         <v>3.7</v>
       </c>
-      <c r="Q16" s="101" t="s">
+      <c r="R16" s="34">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="S16" s="34">
+        <f>R16*L16</f>
+        <v>15.1</v>
+      </c>
+      <c r="T16" s="97" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="114"/>
+      <c r="B17" s="111"/>
       <c r="C17" s="49" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>66</v>
@@ -2991,32 +3115,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="M17" s="14">
+      <c r="N17" s="14">
         <v>0.29597000000000001</v>
       </c>
-      <c r="N17" s="14">
-        <f t="shared" si="1"/>
+      <c r="O17" s="14">
+        <f>N17*J17</f>
         <v>0.29597000000000001</v>
       </c>
-      <c r="O17" s="14">
+      <c r="P17" s="14">
         <v>0.29597000000000001</v>
       </c>
-      <c r="P17" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q17" s="12">
+        <f>P17*K17</f>
         <v>1.4798500000000001</v>
       </c>
-      <c r="Q17" s="102" t="s">
+      <c r="R17" s="12">
+        <v>0.29597000000000001</v>
+      </c>
+      <c r="S17" s="11">
+        <f>R17*L17</f>
+        <v>7.3992500000000003</v>
+      </c>
+      <c r="T17" s="98" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="114"/>
+      <c r="B18" s="111"/>
       <c r="C18" s="45" t="s">
         <v>69</v>
       </c>
@@ -3024,7 +3159,7 @@
         <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>71</v>
@@ -3033,7 +3168,7 @@
         <v>195</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>68</v>
@@ -3045,196 +3180,240 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1.08</v>
       </c>
-      <c r="N18" s="13">
-        <f t="shared" si="1"/>
+      <c r="O18" s="13">
+        <f>N18*J18</f>
         <v>1.08</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1.08</v>
       </c>
-      <c r="P18" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q18" s="11">
+        <f>P18*K18</f>
         <v>5.4</v>
       </c>
-      <c r="Q18" s="99" t="s">
+      <c r="R18" s="11">
+        <v>0.92759999999999998</v>
+      </c>
+      <c r="S18" s="11">
+        <f>R18*L18</f>
+        <v>23.189999999999998</v>
+      </c>
+      <c r="T18" s="96" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="115"/>
-      <c r="C19" s="61" t="s">
-        <v>276</v>
-      </c>
-      <c r="D19" s="62" t="s">
+      <c r="B19" s="112"/>
+      <c r="C19" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="D19" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="I19" s="62" t="s">
+      <c r="H19" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="63">
+      <c r="J19" s="61">
         <v>1</v>
       </c>
-      <c r="K19" s="52">
+      <c r="K19" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L19" s="64" t="s">
+      <c r="L19" s="51">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M19" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="M19" s="65">
+      <c r="N19" s="63">
         <v>0.37</v>
       </c>
-      <c r="N19" s="65">
-        <f t="shared" si="1"/>
+      <c r="O19" s="63">
+        <f>N19*J19</f>
         <v>0.37</v>
       </c>
-      <c r="O19" s="65">
+      <c r="P19" s="63">
         <v>0.37</v>
       </c>
-      <c r="P19" s="66">
-        <f t="shared" si="2"/>
+      <c r="Q19" s="64">
+        <f>P19*K19</f>
         <v>1.85</v>
       </c>
-      <c r="Q19" s="103" t="s">
+      <c r="R19" s="64">
+        <v>0.2868</v>
+      </c>
+      <c r="S19" s="64">
+        <f>R19*L19</f>
+        <v>7.17</v>
+      </c>
+      <c r="T19" s="99" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="110" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="H20" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="J20" s="23">
+      <c r="H20" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="J20" s="31">
         <v>1</v>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L20" s="24" t="s">
+      <c r="L20" s="29">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M20" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M20" s="25">
+      <c r="N20" s="33">
         <v>0.41</v>
       </c>
-      <c r="N20" s="25">
-        <f t="shared" si="1"/>
+      <c r="O20" s="33">
+        <f>N20*J20</f>
         <v>0.41</v>
       </c>
-      <c r="O20" s="25">
+      <c r="P20" s="33">
         <v>0.41</v>
       </c>
-      <c r="P20" s="26">
-        <f t="shared" si="2"/>
+      <c r="Q20" s="34">
+        <f>P20*K20</f>
         <v>2.0499999999999998</v>
       </c>
-      <c r="Q20" s="104"/>
+      <c r="R20" s="34">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S20" s="34">
+        <f>R20*L20</f>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="T20" s="100"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="117"/>
-      <c r="C21" s="67" t="s">
+      <c r="B21" s="112"/>
+      <c r="C21" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="H21" s="68" t="s">
-        <v>267</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="J21" s="17">
+      <c r="H21" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="I21" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="J21" s="61">
         <v>1</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L21" s="56" t="s">
+      <c r="L21" s="51">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M21" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="M21" s="57">
+      <c r="N21" s="63">
         <v>0.64</v>
       </c>
-      <c r="N21" s="57">
-        <f t="shared" si="1"/>
+      <c r="O21" s="63">
+        <f>N21*J21</f>
         <v>0.64</v>
       </c>
-      <c r="O21" s="57">
+      <c r="P21" s="63">
         <v>0.64</v>
       </c>
-      <c r="P21" s="58">
-        <f t="shared" si="2"/>
+      <c r="Q21" s="64">
+        <f>P21*K21</f>
         <v>3.2</v>
       </c>
-      <c r="Q21" s="100"/>
+      <c r="R21" s="64">
+        <v>0.52839999999999998</v>
+      </c>
+      <c r="S21" s="64">
+        <f>R21*L21</f>
+        <v>13.209999999999999</v>
+      </c>
+      <c r="T21" s="102"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="110" t="s">
         <v>251</v>
       </c>
-      <c r="C22" s="69" t="s">
-        <v>278</v>
+      <c r="C22" s="67" t="s">
+        <v>277</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>91</v>
@@ -3261,32 +3440,43 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L22" s="32" t="s">
+      <c r="L22" s="29">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="M22" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M22" s="33">
+      <c r="N22" s="33">
         <v>0.1</v>
       </c>
-      <c r="N22" s="33">
-        <f t="shared" si="1"/>
+      <c r="O22" s="33">
+        <f>N22*J22</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O22" s="33">
+      <c r="P22" s="33">
         <v>2.7E-2</v>
       </c>
-      <c r="P22" s="34">
-        <f t="shared" si="2"/>
+      <c r="Q22" s="34">
+        <f>P22*K22</f>
         <v>0.80999999999999994</v>
       </c>
-      <c r="Q22" s="105"/>
+      <c r="R22" s="34">
+        <v>1.09E-2</v>
+      </c>
+      <c r="S22" s="34">
+        <f>R22*L22</f>
+        <v>1.635</v>
+      </c>
+      <c r="T22" s="100"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="114"/>
+      <c r="B23" s="111"/>
       <c r="C23" s="46" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>95</v>
@@ -3313,32 +3503,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M23" s="13">
+      <c r="N23" s="13">
         <v>0.1</v>
       </c>
-      <c r="N23" s="13">
-        <f t="shared" si="1"/>
+      <c r="O23" s="13">
+        <f>N23*J23</f>
         <v>0.1</v>
       </c>
-      <c r="O23" s="13">
+      <c r="P23" s="13">
         <v>0.1</v>
       </c>
-      <c r="P23" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q23" s="11">
+        <f>P23*K23</f>
         <v>0.5</v>
       </c>
-      <c r="Q23" s="106"/>
+      <c r="R23" s="11">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="S23" s="11">
+        <f>R23*L23</f>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="T23" s="101"/>
     </row>
-    <row r="24" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="114"/>
+      <c r="B24" s="111"/>
       <c r="C24" s="46" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>98</v>
@@ -3353,7 +3554,7 @@
         <v>198</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>97</v>
@@ -3365,32 +3566,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M24" s="13">
+      <c r="N24" s="13">
         <v>0.1</v>
       </c>
-      <c r="N24" s="13">
-        <f t="shared" si="1"/>
+      <c r="O24" s="13">
+        <f>N24*J24</f>
         <v>0.1</v>
       </c>
-      <c r="O24" s="13">
+      <c r="P24" s="13">
         <v>0.1</v>
       </c>
-      <c r="P24" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q24" s="11">
+        <f>P24*K24</f>
         <v>0.5</v>
       </c>
-      <c r="Q24" s="106"/>
+      <c r="R24" s="11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="S24" s="11">
+        <f>R24*L24</f>
+        <v>1.05</v>
+      </c>
+      <c r="T24" s="101"/>
     </row>
-    <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="114"/>
+      <c r="B25" s="111"/>
       <c r="C25" s="46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>101</v>
@@ -3417,32 +3629,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M25" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M25" s="13">
+      <c r="N25" s="13">
         <v>0.1</v>
       </c>
-      <c r="N25" s="13">
-        <f t="shared" si="1"/>
+      <c r="O25" s="13">
+        <f>N25*J25</f>
         <v>0.1</v>
       </c>
-      <c r="O25" s="13">
+      <c r="P25" s="13">
         <v>0.1</v>
       </c>
-      <c r="P25" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q25" s="11">
+        <f>P25*K25</f>
         <v>0.5</v>
       </c>
-      <c r="Q25" s="106"/>
+      <c r="R25" s="11">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="S25" s="11">
+        <f>R25*L25</f>
+        <v>1.625</v>
+      </c>
+      <c r="T25" s="101"/>
     </row>
-    <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="114"/>
+      <c r="B26" s="111"/>
       <c r="C26" s="46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>104</v>
@@ -3469,30 +3692,41 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M26" s="13">
+      <c r="N26" s="13">
         <v>0.1</v>
       </c>
-      <c r="N26" s="13">
-        <f t="shared" si="1"/>
+      <c r="O26" s="13">
+        <f>N26*J26</f>
         <v>0.1</v>
       </c>
-      <c r="O26" s="13">
+      <c r="P26" s="13">
         <v>0.1</v>
       </c>
-      <c r="P26" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q26" s="11">
+        <f>P26*K26</f>
         <v>0.5</v>
       </c>
-      <c r="Q26" s="106"/>
+      <c r="R26" s="11">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="S26" s="11">
+        <f>R26*L26</f>
+        <v>1.325</v>
+      </c>
+      <c r="T26" s="101"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="114"/>
+      <c r="B27" s="111"/>
       <c r="C27" s="45" t="s">
         <v>107</v>
       </c>
@@ -3521,32 +3755,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M27" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M27" s="13">
+      <c r="N27" s="13">
         <v>0.1</v>
       </c>
-      <c r="N27" s="13">
-        <f t="shared" si="1"/>
+      <c r="O27" s="13">
+        <f>N27*J27</f>
         <v>0.1</v>
       </c>
-      <c r="O27" s="13">
+      <c r="P27" s="13">
         <v>0.1</v>
       </c>
-      <c r="P27" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q27" s="11">
+        <f>P27*K27</f>
         <v>0.5</v>
       </c>
-      <c r="Q27" s="106"/>
+      <c r="R27" s="11">
+        <v>2.7E-2</v>
+      </c>
+      <c r="S27" s="11">
+        <f>R27*L27</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="T27" s="101"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="114"/>
+      <c r="B28" s="111"/>
       <c r="C28" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>111</v>
@@ -3573,32 +3818,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M28" s="13">
+      <c r="N28" s="13">
         <v>0.1</v>
       </c>
-      <c r="N28" s="13">
-        <f t="shared" si="1"/>
+      <c r="O28" s="13">
+        <f>N28*J28</f>
         <v>0.1</v>
       </c>
-      <c r="O28" s="13">
+      <c r="P28" s="13">
         <v>0.1</v>
       </c>
-      <c r="P28" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q28" s="11">
+        <f>P28*K28</f>
         <v>0.5</v>
       </c>
-      <c r="Q28" s="106"/>
+      <c r="R28" s="11">
+        <v>7.8E-2</v>
+      </c>
+      <c r="S28" s="11">
+        <f>R28*L28</f>
+        <v>1.95</v>
+      </c>
+      <c r="T28" s="101"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="114"/>
+      <c r="B29" s="111"/>
       <c r="C29" s="46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>114</v>
@@ -3613,7 +3869,7 @@
         <v>199</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>113</v>
@@ -3625,32 +3881,43 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M29" s="13">
+      <c r="N29" s="13">
         <v>0.1</v>
       </c>
-      <c r="N29" s="13">
-        <f t="shared" si="1"/>
+      <c r="O29" s="13">
+        <f>N29*J29</f>
         <v>0.2</v>
       </c>
-      <c r="O29" s="13">
+      <c r="P29" s="13">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="P29" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q29" s="11">
+        <f>P29*K29</f>
         <v>0.18</v>
       </c>
-      <c r="Q29" s="106"/>
+      <c r="R29" s="11">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="S29" s="11">
+        <f>R29*L29</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="T29" s="101"/>
     </row>
-    <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="114"/>
+      <c r="B30" s="111"/>
       <c r="C30" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>117</v>
@@ -3665,7 +3932,7 @@
         <v>198</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>116</v>
@@ -3677,30 +3944,41 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M30" s="13">
+      <c r="N30" s="13">
         <v>0.1</v>
       </c>
-      <c r="N30" s="13">
-        <f t="shared" si="1"/>
+      <c r="O30" s="13">
+        <f>N30*J30</f>
         <v>0.1</v>
       </c>
-      <c r="O30" s="13">
+      <c r="P30" s="13">
         <v>0.1</v>
       </c>
-      <c r="P30" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q30" s="11">
+        <f>P30*K30</f>
         <v>0.5</v>
       </c>
-      <c r="Q30" s="106"/>
+      <c r="R30" s="11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="S30" s="11">
+        <f>R30*L30</f>
+        <v>1.05</v>
+      </c>
+      <c r="T30" s="101"/>
     </row>
-    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="114"/>
+      <c r="B31" s="111"/>
       <c r="C31" s="45" t="s">
         <v>120</v>
       </c>
@@ -3729,32 +4007,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M31" s="13">
+      <c r="N31" s="13">
         <v>0.1</v>
       </c>
-      <c r="N31" s="13">
-        <f t="shared" si="1"/>
+      <c r="O31" s="13">
+        <f>N31*J31</f>
         <v>0.1</v>
       </c>
-      <c r="O31" s="13">
+      <c r="P31" s="13">
         <v>0.1</v>
       </c>
-      <c r="P31" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q31" s="11">
+        <f>P31*K31</f>
         <v>0.5</v>
       </c>
-      <c r="Q31" s="106"/>
+      <c r="R31" s="11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="S31" s="11">
+        <f>R31*L31</f>
+        <v>1.05</v>
+      </c>
+      <c r="T31" s="101"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="114"/>
+      <c r="B32" s="111"/>
       <c r="C32" s="46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>123</v>
@@ -3769,7 +4058,7 @@
         <v>186</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>90</v>
@@ -3781,30 +4070,41 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M32" s="13">
+      <c r="N32" s="13">
         <v>0.31</v>
       </c>
-      <c r="N32" s="13">
-        <f t="shared" si="1"/>
+      <c r="O32" s="13">
+        <f>N32*J32</f>
         <v>0.31</v>
       </c>
-      <c r="O32" s="13">
+      <c r="P32" s="13">
         <v>0.31</v>
       </c>
-      <c r="P32" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q32" s="11">
+        <f>P32*K32</f>
         <v>1.55</v>
       </c>
-      <c r="Q32" s="106"/>
+      <c r="R32" s="11">
+        <v>0.21879999999999999</v>
+      </c>
+      <c r="S32" s="11">
+        <f>R32*L32</f>
+        <v>5.47</v>
+      </c>
+      <c r="T32" s="101"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="114"/>
+      <c r="B33" s="111"/>
       <c r="C33" s="45" t="s">
         <v>126</v>
       </c>
@@ -3833,250 +4133,305 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M33" s="13">
+      <c r="N33" s="13">
         <v>0.1</v>
       </c>
-      <c r="N33" s="13">
-        <f t="shared" si="1"/>
+      <c r="O33" s="13">
+        <f>N33*J33</f>
         <v>0.1</v>
       </c>
-      <c r="O33" s="13">
+      <c r="P33" s="13">
         <v>0.1</v>
       </c>
-      <c r="P33" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q33" s="11">
+        <f>P33*K33</f>
         <v>0.5</v>
       </c>
-      <c r="Q33" s="106"/>
+      <c r="R33" s="11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="S33" s="11">
+        <f>R33*L33</f>
+        <v>1.05</v>
+      </c>
+      <c r="T33" s="101"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="115"/>
-      <c r="C34" s="61" t="s">
-        <v>288</v>
-      </c>
-      <c r="D34" s="62" t="s">
+      <c r="B34" s="112"/>
+      <c r="C34" s="59" t="s">
+        <v>287</v>
+      </c>
+      <c r="D34" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="E34" s="62" t="s">
+      <c r="E34" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="62" t="s">
+      <c r="F34" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="G34" s="52" t="s">
+      <c r="G34" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="H34" s="52" t="s">
+      <c r="H34" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="I34" s="62" t="s">
+      <c r="I34" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="J34" s="63">
+      <c r="J34" s="61">
         <v>1</v>
       </c>
-      <c r="K34" s="52">
+      <c r="K34" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L34" s="64" t="s">
+      <c r="L34" s="51">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M34" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="M34" s="65">
+      <c r="N34" s="63">
         <v>0.1</v>
       </c>
-      <c r="N34" s="65">
-        <f t="shared" si="1"/>
+      <c r="O34" s="63">
+        <f>N34*J34</f>
         <v>0.1</v>
       </c>
-      <c r="O34" s="65">
+      <c r="P34" s="63">
         <v>0.1</v>
       </c>
-      <c r="P34" s="66">
-        <f t="shared" si="2"/>
+      <c r="Q34" s="64">
+        <f>P34*K34</f>
         <v>0.5</v>
       </c>
-      <c r="Q34" s="107"/>
+      <c r="R34" s="64">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="S34" s="64">
+        <f>R34*L34</f>
+        <v>1.05</v>
+      </c>
+      <c r="T34" s="102"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="D35" s="73" t="s">
+      <c r="D35" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="E35" s="73" t="s">
-        <v>277</v>
-      </c>
-      <c r="F35" s="73" t="s">
+      <c r="E35" s="71" t="s">
+        <v>276</v>
+      </c>
+      <c r="F35" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="G35" s="74" t="s">
+      <c r="G35" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="H35" s="75" t="s">
-        <v>289</v>
-      </c>
-      <c r="I35" s="73" t="s">
-        <v>273</v>
-      </c>
-      <c r="J35" s="76">
+      <c r="H35" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="I35" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="J35" s="74">
         <v>1</v>
       </c>
-      <c r="K35" s="74">
+      <c r="K35" s="72">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L35" s="77" t="s">
+      <c r="L35" s="72">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M35" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="M35" s="78">
+      <c r="N35" s="76">
         <v>0.96</v>
       </c>
-      <c r="N35" s="78">
-        <f t="shared" si="1"/>
+      <c r="O35" s="76">
+        <f>N35*J35</f>
         <v>0.96</v>
       </c>
-      <c r="O35" s="78">
+      <c r="P35" s="76">
         <v>0.96</v>
       </c>
-      <c r="P35" s="79">
-        <f t="shared" si="2"/>
+      <c r="Q35" s="77">
+        <f>P35*K35</f>
         <v>4.8</v>
       </c>
-      <c r="Q35" s="108" t="s">
+      <c r="R35" s="77">
+        <v>0.86639999999999995</v>
+      </c>
+      <c r="S35" s="77">
+        <f>R35*L35</f>
+        <v>21.66</v>
+      </c>
+      <c r="T35" s="103" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="78" t="s">
         <v>253</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="C36" s="79" t="s">
+        <v>289</v>
+      </c>
+      <c r="D36" s="80" t="s">
         <v>290</v>
       </c>
-      <c r="D36" s="82" t="s">
+      <c r="E36" s="80" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="80" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="E36" s="82" t="s">
-        <v>277</v>
-      </c>
-      <c r="F36" s="82" t="s">
-        <v>138</v>
-      </c>
-      <c r="G36" s="83" t="s">
-        <v>194</v>
-      </c>
-      <c r="H36" s="84" t="s">
-        <v>292</v>
-      </c>
-      <c r="I36" s="82" t="s">
-        <v>273</v>
-      </c>
-      <c r="J36" s="85">
+      <c r="I36" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="J36" s="83">
         <v>1</v>
       </c>
-      <c r="K36" s="83">
+      <c r="K36" s="81">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L36" s="86" t="s">
+      <c r="L36" s="81">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M36" s="84" t="s">
         <v>187</v>
       </c>
-      <c r="M36" s="87">
+      <c r="N36" s="85">
         <v>0.56000000000000005</v>
       </c>
-      <c r="N36" s="87">
-        <f t="shared" si="1"/>
+      <c r="O36" s="85">
+        <f>N36*J36</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="O36" s="87">
+      <c r="P36" s="85">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P36" s="88">
-        <f t="shared" si="2"/>
+      <c r="Q36" s="86">
+        <f>P36*K36</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="Q36" s="109"/>
+      <c r="R36" s="86">
+        <v>0.46479999999999999</v>
+      </c>
+      <c r="S36" s="86">
+        <f>R36*L36</f>
+        <v>11.62</v>
+      </c>
+      <c r="T36" s="104"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="113" t="s">
+      <c r="B37" s="111" t="s">
         <v>254</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E37" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="F37" s="28" t="s">
+      <c r="E37" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F37" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="G37" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="H37" s="30" t="s">
+      <c r="G37" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="I37" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="J37" s="31">
+      <c r="H37" s="57" t="s">
+        <v>291</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="J37" s="23">
         <v>1</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="22">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L37" s="32" t="s">
+      <c r="L37" s="22">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M37" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="M37" s="33">
+      <c r="N37" s="25">
         <v>4.95</v>
       </c>
-      <c r="N37" s="33">
-        <f t="shared" si="1"/>
+      <c r="O37" s="25">
+        <f>N37*J37</f>
         <v>4.95</v>
       </c>
-      <c r="O37" s="33">
+      <c r="P37" s="25">
         <v>4.95</v>
       </c>
-      <c r="P37" s="34">
-        <f t="shared" si="2"/>
+      <c r="Q37" s="26">
+        <f>P37*K37</f>
         <v>24.75</v>
       </c>
-      <c r="Q37" s="101" t="s">
+      <c r="R37" s="26">
+        <v>4.95</v>
+      </c>
+      <c r="S37" s="26">
+        <f>R37*L37</f>
+        <v>123.75</v>
+      </c>
+      <c r="T37" s="95" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="111"/>
       <c r="C38" s="45" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>143</v>
@@ -4091,10 +4446,10 @@
         <v>217</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J38" s="5">
         <v>1</v>
@@ -4103,30 +4458,41 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="M38" s="13">
+      <c r="N38" s="13">
         <v>2.1254900000000001</v>
       </c>
-      <c r="N38" s="13">
-        <f t="shared" si="1"/>
+      <c r="O38" s="13">
+        <f>N38*J38</f>
         <v>2.1254900000000001</v>
       </c>
-      <c r="O38" s="13">
+      <c r="P38" s="13">
         <v>2.1254900000000001</v>
       </c>
-      <c r="P38" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q38" s="11">
+        <f>P38*K38</f>
         <v>10.62745</v>
       </c>
-      <c r="Q38" s="99"/>
+      <c r="R38" s="11">
+        <v>1.7655099999999999</v>
+      </c>
+      <c r="S38" s="11">
+        <f>R38*L38</f>
+        <v>44.137749999999997</v>
+      </c>
+      <c r="T38" s="96"/>
     </row>
-    <row r="39" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="111"/>
       <c r="C39" s="45" t="s">
         <v>146</v>
       </c>
@@ -4143,10 +4509,10 @@
         <v>203</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J39" s="5">
         <v>1</v>
@@ -4155,32 +4521,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="L39" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M39" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M39" s="13">
+      <c r="N39" s="13">
         <v>13.55</v>
       </c>
-      <c r="N39" s="13">
-        <f t="shared" si="1"/>
+      <c r="O39" s="13">
+        <f>N39*J39</f>
         <v>13.55</v>
       </c>
-      <c r="O39" s="13">
+      <c r="P39" s="13">
         <v>13.55</v>
       </c>
-      <c r="P39" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q39" s="11">
+        <f>P39*K39</f>
         <v>67.75</v>
       </c>
-      <c r="Q39" s="99" t="s">
+      <c r="R39" s="11">
+        <v>7.04</v>
+      </c>
+      <c r="S39" s="11">
+        <f>R39*L39</f>
+        <v>176</v>
+      </c>
+      <c r="T39" s="96" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="111"/>
       <c r="C40" s="45" t="s">
         <v>150</v>
       </c>
@@ -4197,10 +4574,10 @@
         <v>204</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J40" s="5">
         <v>1</v>
@@ -4209,32 +4586,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M40" s="13">
+      <c r="N40" s="13">
         <v>0.61</v>
       </c>
-      <c r="N40" s="13">
-        <f t="shared" si="1"/>
+      <c r="O40" s="13">
+        <f>N40*J40</f>
         <v>0.61</v>
       </c>
-      <c r="O40" s="13">
+      <c r="P40" s="13">
         <v>0.61</v>
       </c>
-      <c r="P40" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q40" s="11">
+        <f>P40*K40</f>
         <v>3.05</v>
       </c>
-      <c r="Q40" s="99" t="s">
+      <c r="R40" s="11">
+        <v>0.58479999999999999</v>
+      </c>
+      <c r="S40" s="11">
+        <f>R40*L40</f>
+        <v>14.62</v>
+      </c>
+      <c r="T40" s="96" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="111"/>
       <c r="C41" s="45" t="s">
         <v>154</v>
       </c>
@@ -4251,10 +4639,10 @@
         <v>216</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J41" s="5">
         <v>1</v>
@@ -4263,34 +4651,45 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M41" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="M41" s="13">
+      <c r="N41" s="13">
         <v>0.53007000000000004</v>
       </c>
-      <c r="N41" s="13">
-        <f t="shared" si="1"/>
+      <c r="O41" s="13">
+        <f>N41*J41</f>
         <v>0.53007000000000004</v>
       </c>
-      <c r="O41" s="13">
+      <c r="P41" s="13">
         <v>0.53007000000000004</v>
       </c>
-      <c r="P41" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q41" s="11">
+        <f>P41*K41</f>
         <v>2.6503500000000004</v>
       </c>
-      <c r="Q41" s="99" t="s">
+      <c r="R41" s="11">
+        <v>0.53007000000000004</v>
+      </c>
+      <c r="S41" s="11">
+        <f>R41*L41</f>
+        <v>13.251750000000001</v>
+      </c>
+      <c r="T41" s="96" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="111"/>
       <c r="C42" s="45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>158</v>
@@ -4305,10 +4704,10 @@
         <v>215</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J42" s="5">
         <v>1</v>
@@ -4317,32 +4716,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="M42" s="13">
-        <v>0.2616</v>
-      </c>
       <c r="N42" s="13">
-        <f t="shared" si="1"/>
-        <v>0.2616</v>
+        <v>0.5232</v>
       </c>
       <c r="O42" s="13">
-        <v>0.2616</v>
-      </c>
-      <c r="P42" s="11">
-        <f t="shared" si="2"/>
-        <v>1.3080000000000001</v>
-      </c>
-      <c r="Q42" s="99" t="s">
+        <f>N42*J42</f>
+        <v>0.5232</v>
+      </c>
+      <c r="P42" s="13">
+        <v>0.5232</v>
+      </c>
+      <c r="Q42" s="11">
+        <f>P42*K42</f>
+        <v>2.6160000000000001</v>
+      </c>
+      <c r="R42" s="11">
+        <v>0.5232</v>
+      </c>
+      <c r="S42" s="11">
+        <f>R42*L42</f>
+        <v>13.08</v>
+      </c>
+      <c r="T42" s="96" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="114"/>
+      <c r="B43" s="111"/>
       <c r="C43" s="45" t="s">
         <v>161</v>
       </c>
@@ -4359,10 +4769,10 @@
         <v>204</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J43" s="5">
         <v>1</v>
@@ -4371,32 +4781,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M43" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M43" s="13">
+      <c r="N43" s="13">
         <v>0.79</v>
       </c>
-      <c r="N43" s="13">
-        <f t="shared" si="1"/>
+      <c r="O43" s="13">
+        <f>N43*J43</f>
         <v>0.79</v>
       </c>
-      <c r="O43" s="13">
+      <c r="P43" s="13">
         <v>0.79</v>
       </c>
-      <c r="P43" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q43" s="11">
+        <f>P43*K43</f>
         <v>3.95</v>
       </c>
-      <c r="Q43" s="99" t="s">
+      <c r="R43" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="S43" s="11">
+        <f>R43*L43</f>
+        <v>16.25</v>
+      </c>
+      <c r="T43" s="96" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="114"/>
+      <c r="B44" s="111"/>
       <c r="C44" s="45" t="s">
         <v>165</v>
       </c>
@@ -4413,10 +4834,10 @@
         <v>197</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J44" s="5">
         <v>1</v>
@@ -4425,94 +4846,116 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M44" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M44" s="13">
+      <c r="N44" s="13">
         <v>0.56000000000000005</v>
       </c>
-      <c r="N44" s="13">
-        <f t="shared" si="1"/>
+      <c r="O44" s="13">
+        <f>N44*J44</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="O44" s="13">
+      <c r="P44" s="13">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P44" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q44" s="11">
+        <f>P44*K44</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="Q44" s="99" t="s">
+      <c r="R44" s="11">
+        <v>0.44879999999999998</v>
+      </c>
+      <c r="S44" s="11">
+        <f>R44*L44</f>
+        <v>11.219999999999999</v>
+      </c>
+      <c r="T44" s="96" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="115"/>
-      <c r="C45" s="70" t="s">
+      <c r="B45" s="111"/>
+      <c r="C45" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="D45" s="62" t="s">
+      <c r="D45" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="G45" s="52" t="s">
+      <c r="G45" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="H45" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="I45" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="J45" s="63">
+      <c r="H45" s="66" t="s">
+        <v>291</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="J45" s="17">
         <v>1</v>
       </c>
-      <c r="K45" s="52">
+      <c r="K45" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L45" s="64" t="s">
+      <c r="L45" s="16">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M45" s="54" t="s">
         <v>187</v>
       </c>
-      <c r="M45" s="65">
+      <c r="N45" s="55">
         <v>2.19</v>
       </c>
-      <c r="N45" s="65">
-        <f t="shared" si="1"/>
+      <c r="O45" s="55">
+        <f>N45*J45</f>
         <v>2.19</v>
       </c>
-      <c r="O45" s="65">
+      <c r="P45" s="55">
         <v>2.19</v>
       </c>
-      <c r="P45" s="66">
-        <f t="shared" si="2"/>
+      <c r="Q45" s="56">
+        <f>P45*K45</f>
         <v>10.95</v>
       </c>
-      <c r="Q45" s="103"/>
+      <c r="R45" s="56">
+        <v>1.8552</v>
+      </c>
+      <c r="S45" s="56">
+        <f>R45*L45</f>
+        <v>46.379999999999995</v>
+      </c>
+      <c r="T45" s="106"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="113" t="s">
+      <c r="B46" s="110" t="s">
         <v>255</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="58" t="s">
         <v>49</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F46" s="28" t="s">
         <v>48</v>
@@ -4521,10 +4964,10 @@
         <v>206</v>
       </c>
       <c r="H46" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J46" s="31">
         <v>1</v>
@@ -4533,40 +4976,51 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L46" s="32" t="s">
+      <c r="L46" s="29">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M46" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="M46" s="33">
+      <c r="N46" s="33">
         <v>1.19</v>
       </c>
-      <c r="N46" s="33">
-        <f t="shared" si="1"/>
+      <c r="O46" s="33">
+        <f>N46*J46</f>
         <v>1.19</v>
       </c>
-      <c r="O46" s="33">
+      <c r="P46" s="33">
         <v>1.19</v>
       </c>
-      <c r="P46" s="34">
-        <f t="shared" si="2"/>
+      <c r="Q46" s="34">
+        <f>P46*K46</f>
         <v>5.9499999999999993</v>
       </c>
-      <c r="Q46" s="101" t="s">
+      <c r="R46" s="34">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="S46" s="34">
+        <f>R46*L46</f>
+        <v>24.6</v>
+      </c>
+      <c r="T46" s="97" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="114"/>
+      <c r="B47" s="111"/>
       <c r="C47" s="45" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>60</v>
@@ -4575,10 +5029,10 @@
         <v>238</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J47" s="5">
         <v>1</v>
@@ -4587,32 +5041,43 @@
         <f>J47*5</f>
         <v>5</v>
       </c>
-      <c r="L47" s="6" t="s">
+      <c r="L47" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M47" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="M47" s="13">
+      <c r="N47" s="13">
         <v>8.8000000000000007</v>
       </c>
-      <c r="N47" s="13">
-        <f t="shared" si="1"/>
+      <c r="O47" s="13">
+        <f>N47*J47</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="O47" s="13">
+      <c r="P47" s="13">
         <v>8.8000000000000007</v>
       </c>
-      <c r="P47" s="11">
-        <f t="shared" si="2"/>
+      <c r="Q47" s="11">
+        <f>P47*K47</f>
         <v>44</v>
       </c>
-      <c r="Q47" s="99" t="s">
+      <c r="R47" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="S47" s="11">
+        <f>R47*L47</f>
+        <v>220.00000000000003</v>
+      </c>
+      <c r="T47" s="96" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="114"/>
+      <c r="B48" s="111"/>
       <c r="C48" s="45" t="s">
         <v>58</v>
       </c>
@@ -4620,7 +5085,7 @@
         <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>57</v>
@@ -4629,10 +5094,10 @@
         <v>207</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J48" s="5">
         <v>1</v>
@@ -4641,8 +5106,9 @@
         <f>J48*5</f>
         <v>5</v>
       </c>
-      <c r="L48" s="2" t="s">
-        <v>245</v>
+      <c r="L48" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>245</v>
@@ -4656,15 +5122,23 @@
       <c r="P48" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="Q48" s="50" t="s">
+      <c r="Q48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="R48" s="2"/>
+      <c r="S48" s="11">
+        <f>R48*L48</f>
+        <v>0</v>
+      </c>
+      <c r="T48" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="114"/>
+      <c r="B49" s="111"/>
       <c r="C49" s="45" t="s">
         <v>52</v>
       </c>
@@ -4678,13 +5152,13 @@
         <v>51</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J49" s="5">
         <v>1</v>
@@ -4693,14 +5167,15 @@
         <f>J49*5</f>
         <v>5</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>245</v>
@@ -4708,15 +5183,23 @@
       <c r="P49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="Q49" s="50" t="s">
+      <c r="Q49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="R49" s="2"/>
+      <c r="S49" s="11">
+        <f>R49*L49</f>
+        <v>0</v>
+      </c>
+      <c r="T49" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="114"/>
+      <c r="B50" s="111"/>
       <c r="C50" s="45" t="s">
         <v>55</v>
       </c>
@@ -4730,13 +5213,13 @@
         <v>54</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J50" s="5">
         <v>2</v>
@@ -4745,14 +5228,15 @@
         <f>J50*5</f>
         <v>10</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>245</v>
@@ -4760,15 +5244,23 @@
       <c r="P50" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="Q50" s="50" t="s">
+      <c r="Q50" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="R50" s="2"/>
+      <c r="S50" s="11">
+        <f>R50*L50</f>
+        <v>0</v>
+      </c>
+      <c r="T50" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="114"/>
+      <c r="B51" s="111"/>
       <c r="C51" s="45" t="s">
         <v>79</v>
       </c>
@@ -4782,13 +5274,13 @@
         <v>81</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J51" s="5">
         <v>1</v>
@@ -4797,14 +5289,15 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="L51" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M51" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="N51" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>245</v>
@@ -4812,192 +5305,215 @@
       <c r="P51" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="Q51" s="50" t="s">
+      <c r="Q51" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="R51" s="2"/>
+      <c r="S51" s="11">
+        <f>R51*L51</f>
+        <v>0</v>
+      </c>
+      <c r="T51" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="115"/>
-      <c r="C52" s="89" t="s">
+      <c r="B52" s="112"/>
+      <c r="C52" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="D52" s="90" t="s">
+      <c r="D52" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="E52" s="62" t="s">
+      <c r="E52" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="F52" s="62" t="s">
+      <c r="F52" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="G52" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="H52" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="I52" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="J52" s="63">
+      <c r="G52" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="H52" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="I52" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="J52" s="61">
         <v>14</v>
       </c>
-      <c r="K52" s="52">
+      <c r="K52" s="51">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="L52" s="91" t="s">
+      <c r="L52" s="51">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="M52" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="M52" s="91" t="s">
+      <c r="N52" s="89" t="s">
         <v>246</v>
       </c>
-      <c r="N52" s="91" t="s">
+      <c r="O52" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="O52" s="91" t="s">
+      <c r="P52" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="P52" s="91" t="s">
+      <c r="Q52" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="Q52" s="54" t="s">
+      <c r="R52" s="89"/>
+      <c r="S52" s="64">
+        <f>R52*L52</f>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="71" t="s">
+      <c r="B53" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="C53" s="92" t="s">
+      <c r="C53" s="90" t="s">
         <v>258</v>
       </c>
-      <c r="D53" s="74" t="s">
+      <c r="D53" s="72" t="s">
         <v>257</v>
       </c>
-      <c r="E53" s="74" t="s">
-        <v>277</v>
-      </c>
-      <c r="F53" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G53" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="H53" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="I53" s="73" t="s">
-        <v>273</v>
-      </c>
-      <c r="J53" s="74">
+      <c r="E53" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="F53" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="G53" s="73" t="s">
+        <v>291</v>
+      </c>
+      <c r="H53" s="73" t="s">
+        <v>291</v>
+      </c>
+      <c r="I53" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="J53" s="72">
         <v>1</v>
       </c>
-      <c r="K53" s="74">
+      <c r="K53" s="72">
         <v>5</v>
       </c>
-      <c r="L53" s="74"/>
-      <c r="M53" s="74"/>
-      <c r="N53" s="74"/>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
-      <c r="Q53" s="93" t="s">
+      <c r="L53" s="72">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M53" s="72"/>
+      <c r="N53" s="72"/>
+      <c r="O53" s="72"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="77">
+        <f>R53*L53</f>
+        <v>0</v>
+      </c>
+      <c r="T53" s="91" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="78" t="s">
         <v>259</v>
       </c>
+      <c r="C54" s="92"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="81" t="s">
+        <v>276</v>
+      </c>
+      <c r="F54" s="93"/>
+      <c r="G54" s="82" t="s">
+        <v>291</v>
+      </c>
+      <c r="H54" s="82" t="s">
+        <v>291</v>
+      </c>
+      <c r="I54" s="93"/>
+      <c r="J54" s="93"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="93"/>
+      <c r="M54" s="93"/>
+      <c r="N54" s="93"/>
+      <c r="O54" s="93"/>
+      <c r="P54" s="93"/>
+      <c r="Q54" s="93"/>
+      <c r="R54" s="93"/>
+      <c r="S54" s="93"/>
+      <c r="T54" s="94" t="s">
+        <v>260</v>
+      </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="51">
-        <v>52</v>
-      </c>
-      <c r="B54" s="80" t="s">
-        <v>260</v>
-      </c>
-      <c r="C54" s="94"/>
-      <c r="D54" s="95"/>
-      <c r="E54" s="83" t="s">
-        <v>277</v>
-      </c>
-      <c r="F54" s="95"/>
-      <c r="G54" s="84" t="s">
-        <v>292</v>
-      </c>
-      <c r="H54" s="84" t="s">
-        <v>292</v>
-      </c>
-      <c r="I54" s="95"/>
-      <c r="J54" s="95"/>
-      <c r="K54" s="95"/>
-      <c r="L54" s="95"/>
-      <c r="M54" s="95"/>
-      <c r="N54" s="95"/>
-      <c r="O54" s="95"/>
-      <c r="P54" s="95"/>
-      <c r="Q54" s="96" t="s">
+    <row r="55" spans="1:20" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I55" t="s">
+        <v>300</v>
+      </c>
+      <c r="J55" s="107" t="s">
         <v>261</v>
       </c>
+      <c r="K55" s="107"/>
+      <c r="L55" s="107"/>
+      <c r="M55" s="107"/>
+      <c r="N55" s="107"/>
+      <c r="Q55" s="19">
+        <f>SUM(Q3:Q47)</f>
+        <v>249.07964999999999</v>
+      </c>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
     </row>
-    <row r="55" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J55" s="118" t="s">
+    <row r="56" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="109"/>
+      <c r="J56" s="108" t="s">
         <v>262</v>
       </c>
-      <c r="K55" s="118"/>
-      <c r="L55" s="118"/>
-      <c r="M55" s="118"/>
-      <c r="P55" s="19">
-        <f>SUM(P3:P47)</f>
-        <v>247.77164999999997</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J56" s="119" t="s">
-        <v>263</v>
-      </c>
-      <c r="K56" s="119"/>
-      <c r="L56" s="119"/>
-      <c r="M56" s="119"/>
-      <c r="N56" s="18">
-        <f>SUM(N3:N47)</f>
-        <v>53.327129999999997</v>
-      </c>
-      <c r="P56" s="19">
-        <f>P55/5</f>
-        <v>49.554329999999993</v>
-      </c>
+      <c r="K56" s="108"/>
+      <c r="L56" s="108"/>
+      <c r="M56" s="108"/>
+      <c r="N56" s="108"/>
+      <c r="O56" s="18">
+        <f>SUM(O3:O47)</f>
+        <v>53.588729999999998</v>
+      </c>
+      <c r="Q56" s="19">
+        <f>Q55/5</f>
+        <v>49.815929999999994</v>
+      </c>
+      <c r="R56" s="19"/>
+      <c r="S56" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
     <mergeCell ref="B22:B34"/>
     <mergeCell ref="B37:B45"/>
     <mergeCell ref="B46:B52"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B3:B12"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
-  <conditionalFormatting sqref="N56:P56">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8DBC2746-D05D-466B-8B7A-FA58F46E438D}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N46">
+  <conditionalFormatting sqref="O3:O46">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -5011,8 +5527,22 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P46">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="Q47:R47">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C278911A-9E5B-49E0-8DC6-15171E4375C7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:S3 Q4:R46 S4:S53">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5025,8 +5555,22 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K54">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="O56:S56">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8DBC2746-D05D-466B-8B7A-FA58F46E438D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:L54">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5037,100 +5581,73 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P47">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C278911A-9E5B-49E0-8DC6-15171E4375C7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="L5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G11" r:id="rId5" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G12" r:id="rId6" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="L13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="L14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="L18" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="L20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="L21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="L24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="L29" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="L30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="L35" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="L45" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G6" r:id="rId17" display="https://lcsc.com/brand-detail/79.html" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="L6" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="L7" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="L9" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="L10" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L11" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="L12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G31" r:id="rId24" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="G44" r:id="rId25" display="https://lcsc.com/brand-detail/296.html" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="G42" r:id="rId26" display="https://lcsc.com/brand-detail/488.html" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="G41" r:id="rId27" display="https://lcsc.com/brand-detail/897.html" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="G38" r:id="rId28" display="https://lcsc.com/brand-detail/11667.html" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G28" r:id="rId29" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="G26" r:id="rId30" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="G25" r:id="rId31" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="G22" r:id="rId32" display="https://lcsc.com/brand-detail/512.html" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="G17" r:id="rId33" display="https://lcsc.com/brand-detail/11934.html" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="L15" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="L16" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="L19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="L22" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="L23" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="L25" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="L26" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L27" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="L28" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="L31" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="G32" r:id="rId44" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="L32" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="L33" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="L34" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="L36" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="L37" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L39" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="L40" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="L43" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="L44" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="L46" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="G47" r:id="rId55" tooltip="Magnetic Connectors from HytePro" display="https://www.hyte.pro/" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="L38" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L42" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="L41" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="L17" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="L47" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="M3" r:id="rId1"/>
+    <hyperlink ref="M4" r:id="rId2"/>
+    <hyperlink ref="M5" r:id="rId3"/>
+    <hyperlink ref="M8" r:id="rId4"/>
+    <hyperlink ref="G11" r:id="rId5" display="https://www.digikey.com/en/supplier-centers/murata-electronics"/>
+    <hyperlink ref="G12" r:id="rId6" display="https://www.digikey.com/en/supplier-centers/murata-electronics"/>
+    <hyperlink ref="M13" r:id="rId7"/>
+    <hyperlink ref="M14" r:id="rId8"/>
+    <hyperlink ref="M18" r:id="rId9"/>
+    <hyperlink ref="M20" r:id="rId10"/>
+    <hyperlink ref="M21" r:id="rId11"/>
+    <hyperlink ref="M24" r:id="rId12"/>
+    <hyperlink ref="M29" r:id="rId13"/>
+    <hyperlink ref="M30" r:id="rId14"/>
+    <hyperlink ref="M35" r:id="rId15"/>
+    <hyperlink ref="M45" r:id="rId16"/>
+    <hyperlink ref="G6" r:id="rId17" display="https://lcsc.com/brand-detail/79.html"/>
+    <hyperlink ref="M6" r:id="rId18"/>
+    <hyperlink ref="M7" r:id="rId19"/>
+    <hyperlink ref="M9" r:id="rId20"/>
+    <hyperlink ref="M10" r:id="rId21"/>
+    <hyperlink ref="M11" r:id="rId22"/>
+    <hyperlink ref="M12" r:id="rId23"/>
+    <hyperlink ref="G31" r:id="rId24" display="https://lcsc.com/brand-detail/99.html"/>
+    <hyperlink ref="G44" r:id="rId25" display="https://lcsc.com/brand-detail/296.html"/>
+    <hyperlink ref="G42" r:id="rId26" display="https://lcsc.com/brand-detail/488.html"/>
+    <hyperlink ref="G41" r:id="rId27" display="https://lcsc.com/brand-detail/897.html"/>
+    <hyperlink ref="G38" r:id="rId28" display="https://lcsc.com/brand-detail/11667.html"/>
+    <hyperlink ref="G28" r:id="rId29" display="https://lcsc.com/brand-detail/99.html"/>
+    <hyperlink ref="G26" r:id="rId30" display="https://lcsc.com/brand-detail/99.html"/>
+    <hyperlink ref="G25" r:id="rId31" display="https://lcsc.com/brand-detail/99.html"/>
+    <hyperlink ref="G22" r:id="rId32" display="https://lcsc.com/brand-detail/512.html"/>
+    <hyperlink ref="G17" r:id="rId33" display="https://lcsc.com/brand-detail/11934.html"/>
+    <hyperlink ref="M15" r:id="rId34"/>
+    <hyperlink ref="M16" r:id="rId35"/>
+    <hyperlink ref="M19" r:id="rId36"/>
+    <hyperlink ref="M22" r:id="rId37"/>
+    <hyperlink ref="M23" r:id="rId38"/>
+    <hyperlink ref="M25" r:id="rId39"/>
+    <hyperlink ref="M26" r:id="rId40"/>
+    <hyperlink ref="M27" r:id="rId41"/>
+    <hyperlink ref="M28" r:id="rId42"/>
+    <hyperlink ref="M31" r:id="rId43"/>
+    <hyperlink ref="G32" r:id="rId44" display="https://www.digikey.com/en/supplier-centers/murata-electronics"/>
+    <hyperlink ref="M32" r:id="rId45"/>
+    <hyperlink ref="M33" r:id="rId46"/>
+    <hyperlink ref="M34" r:id="rId47"/>
+    <hyperlink ref="M36" r:id="rId48"/>
+    <hyperlink ref="M37" r:id="rId49"/>
+    <hyperlink ref="M39" r:id="rId50"/>
+    <hyperlink ref="M40" r:id="rId51"/>
+    <hyperlink ref="M43" r:id="rId52"/>
+    <hyperlink ref="M44" r:id="rId53"/>
+    <hyperlink ref="M46" r:id="rId54"/>
+    <hyperlink ref="G47" r:id="rId55" tooltip="Magnetic Connectors from HytePro" display="https://www.hyte.pro/"/>
+    <hyperlink ref="M38" r:id="rId56"/>
+    <hyperlink ref="M42" r:id="rId57"/>
+    <hyperlink ref="M41" r:id="rId58"/>
+    <hyperlink ref="M17" r:id="rId59"/>
+    <hyperlink ref="M47" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId61"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8DBC2746-D05D-466B-8B7A-FA58F46E438D}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>N56:P56</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C4653D46-9E1E-4A9D-9BBE-F1F10435DCED}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -5142,7 +5659,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N46</xm:sqref>
+          <xm:sqref>O3:O46</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C278911A-9E5B-49E0-8DC6-15171E4375C7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>Q47:R47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C5B0272F-C97A-4700-81BF-90C991FA66E7}">
@@ -5155,20 +5685,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P46</xm:sqref>
+          <xm:sqref>Q3:S3 Q4:R46 S4:S53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C278911A-9E5B-49E0-8DC6-15171E4375C7}">
+          <x14:cfRule type="dataBar" id="{8DBC2746-D05D-466B-8B7A-FA58F46E438D}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF008AEF"/>
+              <x14:borderColor rgb="FF63C384"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
               <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P47</xm:sqref>
+          <xm:sqref>O56:S56</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
